--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:19:25+00:00</t>
+    <t>2026-09-30T09:40:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,31 +141,31 @@
     <t>band-niedrig</t>
   </si>
   <si>
-    <t>Bis zu 2.300 € pro Monat</t>
+    <t>Up to €2,300 a month</t>
   </si>
   <si>
     <t>band-mittel</t>
   </si>
   <si>
-    <t>Zwischen 2.300 € und 5.200 € pro Monat</t>
+    <t>Between €2,300 and €5,200 a month</t>
   </si>
   <si>
     <t>band-hoch</t>
   </si>
   <si>
-    <t>5.200 € pro Monat oder mehr</t>
+    <t>€5,200 a month or more</t>
   </si>
   <si>
     <t>weiss-nicht</t>
   </si>
   <si>
-    <t>Ich weiss es nicht</t>
+    <t>Don't know</t>
   </si>
   <si>
     <t>keine-angabe</t>
   </si>
   <si>
-    <t>Möchte ich nicht sagen</t>
+    <t>Prefer not to say</t>
   </si>
 </sst>
 </file>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:40:42+00:00</t>
+    <t>2026-09-30T19:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:42:59+00:00</t>
+    <t>2026-09-30T19:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Netto-Haushaltseinkommen in Kategorien (Q_OECDLIT7a). EUR-Bänder nach IW Köln (Institut der deutschen Wirtschaft, Niehues/Stockhausen).</t>
+    <t>Netto-Haushaltseinkommen in Kategorien (Q_OECDLIT7a). Die ursprüngliche deutsche Übersetzung liegt in de-CH vor (Schweizer PaRIS-Fassung, Bänder bis CHF 3630 / zwischen CHF 3630 und CHF 6050 / ab CHF 6050 pro Monat). Für PCOR-MII sind die Bänder auf deutsche Gehaltsdaten angepasst: EUR-Terzile nach IW Köln (Institut der deutschen Wirtschaft, Niehues/Stockhausen). Das ist KEINE Währungsumrechnung, sondern eine eigenständige Skala — CHF 3630 entspräche grob 3.800 EUR, nicht 2.300 EUR. Weil der Wortlaut damit deutsch und nicht schweizerisch ist, tragen die Designations hier de-DE; die übrigen DEM-Antwortskalen behalten ihren Schweizer Wortlaut nach ADR-005 bewusst bei.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:54:40+00:00</t>
+    <t>2026-10-01T09:59:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T09:59:00+00:00</t>
+    <t>2026-10-01T11:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:16:03+00:00</t>
+    <t>2026-10-01T11:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:25:55+00:00</t>
+    <t>2026-10-01T11:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:30:23+00:00</t>
+    <t>2026-10-01T13:09:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:09:50+00:00</t>
+    <t>2026-10-01T14:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:39:45+00:00</t>
+    <t>2026-10-01T14:59:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:59:54+00:00</t>
+    <t>2026-10-13T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T13:38:01+00:00</t>
+    <t>2026-10-13T14:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dem-einkommen.xlsx
+++ b/CodeSystem-dem-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T14:06:39+00:00</t>
+    <t>2026-10-14T13:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
